--- a/data/trans_camb/P3A_R1-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R1-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,53; 14,24</t>
+          <t>5,71; 13,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,29; 16,25</t>
+          <t>7,64; 16,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,36; 14,47</t>
+          <t>5,55; 14,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 4,3</t>
+          <t>-2,8; 4,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 5,3</t>
+          <t>-1,42; 5,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 12,75</t>
+          <t>4,35; 13,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 8,13</t>
+          <t>2,38; 8,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,16; 9,71</t>
+          <t>4,25; 9,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,05; 12,46</t>
+          <t>5,78; 12,33</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,97; 106,12</t>
+          <t>32,61; 105,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,85; 120,04</t>
+          <t>43,46; 120,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,75; 105,29</t>
+          <t>32,27; 103,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-23,79; 44,41</t>
+          <t>-21,62; 41,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 54,23</t>
+          <t>-11,45; 58,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,35; 130,83</t>
+          <t>35,87; 134,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,25; 65,78</t>
+          <t>16,05; 67,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,42; 78,73</t>
+          <t>28,35; 79,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>40,74; 103,19</t>
+          <t>42,08; 101,03</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,23; 12,14</t>
+          <t>3,81; 11,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,6; 15,91</t>
+          <t>7,45; 15,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 10,71</t>
+          <t>-9,27; 11,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 6,46</t>
+          <t>0,51; 6,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,1; 12,52</t>
+          <t>6,26; 12,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,57; 16,77</t>
+          <t>10,55; 16,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,09; 8,08</t>
+          <t>3,34; 8,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,84; 12,87</t>
+          <t>7,8; 13,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 12,43</t>
+          <t>0,9; 12,72</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,49; 66,67</t>
+          <t>16,65; 63,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,55; 88,89</t>
+          <t>34,66; 89,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,78; 55,75</t>
+          <t>-41,78; 58,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,46; 72,03</t>
+          <t>3,29; 71,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,04; 136,75</t>
+          <t>52,33; 142,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,4; 194,63</t>
+          <t>88,48; 189,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,13; 58,35</t>
+          <t>21,15; 60,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>47,16; 93,58</t>
+          <t>48,69; 94,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,61; 85,29</t>
+          <t>7,01; 89,48</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 6,78</t>
+          <t>-2,52; 6,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 13,37</t>
+          <t>3,12; 13,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,56; 13,07</t>
+          <t>1,71; 13,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 5,69</t>
+          <t>-1,39; 6,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,61; 10,46</t>
+          <t>2,97; 10,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 10,9</t>
+          <t>-6,15; 11,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 5,37</t>
+          <t>-0,94; 5,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,39; 10,55</t>
+          <t>4,59; 10,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 9,57</t>
+          <t>-3,74; 9,92</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 31,82</t>
+          <t>-9,84; 32,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,27; 61,32</t>
+          <t>11,57; 61,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,38; 60,39</t>
+          <t>6,98; 62,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 46,05</t>
+          <t>-8,81; 50,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15,0; 86,37</t>
+          <t>18,04; 89,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-34,02; 82,44</t>
+          <t>-37,64; 84,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 30,89</t>
+          <t>-4,78; 29,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,73; 60,09</t>
+          <t>21,81; 61,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-20,69; 51,41</t>
+          <t>-18,27; 53,49</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 10,43</t>
+          <t>1,62; 10,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,23; 17,37</t>
+          <t>8,98; 17,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 9,08</t>
+          <t>0,7; 9,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 7,27</t>
+          <t>0,8; 6,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,37; 9,63</t>
+          <t>3,07; 9,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 7,53</t>
+          <t>0,34; 7,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,51; 7,48</t>
+          <t>2,1; 7,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,18; 12,38</t>
+          <t>7,05; 12,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 7,01</t>
+          <t>1,32; 6,87</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,25; 50,25</t>
+          <t>5,89; 47,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>35,64; 79,9</t>
+          <t>34,01; 79,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,35; 42,2</t>
+          <t>2,66; 41,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,63; 63,78</t>
+          <t>5,41; 61,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,02; 84,18</t>
+          <t>20,94; 85,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,61; 64,77</t>
+          <t>4,1; 66,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,76; 44,85</t>
+          <t>11,16; 45,3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>37,45; 74,19</t>
+          <t>36,47; 73,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,4; 43,04</t>
+          <t>8,04; 41,7</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,58</t>
+          <t>4,46; 8,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,12; 13,72</t>
+          <t>9,25; 13,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 9,15</t>
+          <t>-0,4; 9,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,68</t>
+          <t>1,13; 4,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,81; 8,33</t>
+          <t>4,63; 8,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,16; 9,93</t>
+          <t>4,0; 9,91</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,27; 6,1</t>
+          <t>3,38; 6,05</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,6; 10,4</t>
+          <t>7,56; 10,44</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,8; 8,84</t>
+          <t>3,67; 8,8</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>20,02; 43,51</t>
+          <t>20,36; 43,8</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>41,62; 69,44</t>
+          <t>42,96; 68,43</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 45,14</t>
+          <t>-0,3; 44,96</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10,48; 41,85</t>
+          <t>8,47; 41,36</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>37,28; 73,99</t>
+          <t>35,58; 73,03</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,86; 88,13</t>
+          <t>33,88; 87,42</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,14; 38,24</t>
+          <t>20,03; 38,89</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>44,28; 66,23</t>
+          <t>43,86; 66,39</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>22,94; 55,89</t>
+          <t>23,41; 55,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P3A_R1-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R1-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,92</t>
+          <t>9,89</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,32</t>
+          <t>10,27</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9,45</t>
+          <t>10,0</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,71; 13,98</t>
+          <t>5,3; 13,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,64; 16,2</t>
+          <t>7,79; 16,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,55; 14,36</t>
+          <t>5,45; 14,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 4,05</t>
+          <t>-2,83; 4,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 5,73</t>
+          <t>-1,5; 6,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,35; 13,04</t>
+          <t>6,65; 13,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 8,25</t>
+          <t>2,44; 8,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,25; 9,72</t>
+          <t>4,1; 9,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,78; 12,33</t>
+          <t>7,09; 12,59</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>74,19%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,61; 105,29</t>
+          <t>29,79; 100,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43,46; 120,67</t>
+          <t>42,61; 119,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,27; 103,16</t>
+          <t>29,08; 102,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,62; 41,99</t>
+          <t>-21,64; 43,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 58,97</t>
+          <t>-11,36; 63,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,87; 134,12</t>
+          <t>50,73; 140,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,05; 67,84</t>
+          <t>16,37; 64,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,35; 79,03</t>
+          <t>26,26; 79,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42,08; 101,03</t>
+          <t>48,14; 103,81</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,56</t>
+          <t>9,67</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,74</t>
+          <t>12,82</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8,64</t>
+          <t>11,23</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 11,54</t>
+          <t>3,98; 12,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,45; 15,95</t>
+          <t>7,36; 15,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 11,19</t>
+          <t>5,48; 14,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 6,45</t>
+          <t>0,65; 6,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,26; 12,53</t>
+          <t>6,03; 12,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,55; 16,68</t>
+          <t>9,55; 15,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 8,27</t>
+          <t>2,94; 8,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,8; 13,02</t>
+          <t>7,71; 12,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 12,72</t>
+          <t>8,8; 13,96</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>133,78%</t>
+          <t>124,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>74,58%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,65; 63,17</t>
+          <t>18,0; 69,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34,66; 89,13</t>
+          <t>33,16; 90,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,78; 58,36</t>
+          <t>24,6; 79,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,29; 71,21</t>
+          <t>5,42; 75,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,33; 142,83</t>
+          <t>51,58; 147,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,48; 189,81</t>
+          <t>80,74; 183,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,15; 60,05</t>
+          <t>16,97; 57,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>48,69; 94,67</t>
+          <t>46,59; 93,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,01; 89,48</t>
+          <t>53,72; 101,79</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7,96</t>
+          <t>7,97</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,16</t>
+          <t>9,58</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,08</t>
+          <t>8,76</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 6,93</t>
+          <t>-2,9; 6,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,12; 13,16</t>
+          <t>2,98; 12,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 13,16</t>
+          <t>3,08; 13,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 6,08</t>
+          <t>-1,66; 6,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,97; 10,85</t>
+          <t>2,82; 10,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 11,0</t>
+          <t>5,69; 13,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 5,33</t>
+          <t>-1,2; 5,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,59; 10,8</t>
+          <t>4,25; 10,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 9,92</t>
+          <t>5,49; 12,12</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>45,71%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 32,65</t>
+          <t>-10,79; 30,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,57; 61,16</t>
+          <t>11,47; 59,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,98; 62,63</t>
+          <t>11,13; 59,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 50,35</t>
+          <t>-11,22; 48,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,04; 89,21</t>
+          <t>15,91; 87,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-37,64; 84,38</t>
+          <t>37,04; 111,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 29,94</t>
+          <t>-5,7; 30,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21,81; 61,84</t>
+          <t>20,5; 63,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-18,27; 53,49</t>
+          <t>26,42; 69,42</t>
         </is>
       </c>
     </row>
@@ -1282,29 +1282,29 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>4,89</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3,98</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,56</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,13</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
           <t>4,98</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,98</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6,56</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,27</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,98</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>9,69</t>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,42</t>
+          <t>4,95</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 10,19</t>
+          <t>1,86; 10,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,98; 17,45</t>
+          <t>9,08; 17,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 9,08</t>
+          <t>1,08; 8,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 6,99</t>
+          <t>0,89; 7,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,07; 9,81</t>
+          <t>3,22; 10,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 7,36</t>
+          <t>2,15; 7,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 7,48</t>
+          <t>2,36; 7,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,05; 12,32</t>
+          <t>7,06; 12,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,87</t>
+          <t>2,59; 7,41</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,89; 47,12</t>
+          <t>6,76; 48,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>34,01; 79,74</t>
+          <t>35,55; 81,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,66; 41,96</t>
+          <t>4,19; 42,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,41; 61,57</t>
+          <t>5,59; 63,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,94; 85,36</t>
+          <t>21,87; 89,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,1; 66,82</t>
+          <t>14,85; 69,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,16; 45,3</t>
+          <t>12,48; 46,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>36,47; 73,99</t>
+          <t>36,99; 74,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,04; 41,7</t>
+          <t>13,67; 44,54</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6,04</t>
+          <t>8,12</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,82</t>
+          <t>9,34</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,87</t>
+          <t>8,69</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,46; 8,73</t>
+          <t>4,29; 8,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,25; 13,67</t>
+          <t>9,26; 13,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 9,17</t>
+          <t>5,79; 10,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,61</t>
+          <t>1,18; 4,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,63; 8,27</t>
+          <t>4,87; 8,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,0; 9,91</t>
+          <t>7,72; 10,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,38; 6,05</t>
+          <t>3,37; 6,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,56; 10,44</t>
+          <t>7,44; 10,39</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,67; 8,8</t>
+          <t>7,32; 10,08</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>53,03%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>20,36; 43,8</t>
+          <t>19,46; 44,61</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>42,96; 68,43</t>
+          <t>42,03; 68,57</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 44,96</t>
+          <t>26,6; 51,58</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8,47; 41,36</t>
+          <t>9,34; 42,64</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>35,58; 73,03</t>
+          <t>38,28; 75,97</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,88; 87,42</t>
+          <t>59,18; 97,66</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,03; 38,89</t>
+          <t>19,96; 39,27</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>43,86; 66,39</t>
+          <t>43,92; 67,32</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>23,41; 55,2</t>
+          <t>42,71; 63,97</t>
         </is>
       </c>
     </row>
